--- a/upload files/Tracks.xlsx
+++ b/upload files/Tracks.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10102"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10621"/>
   <workbookPr updateLinks="always"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/aaronbell/Desktop/Git Repo Clone/CrewOps360/upload files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CAB37A9C-7E5B-DD4D-AB12-DB4DCD9D8ACA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1C492AC-F23B-F442-8C1B-FC63F440369F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="740" windowWidth="29040" windowHeight="17240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="680" windowWidth="29040" windowHeight="17240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="3" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1526" uniqueCount="159">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1529" uniqueCount="162">
   <si>
     <t>STAFF NAME</t>
   </si>
@@ -514,6 +514,15 @@
   </si>
   <si>
     <t>Saraceno</t>
+  </si>
+  <si>
+    <t>O'Flaherty</t>
+  </si>
+  <si>
+    <t>Phelan</t>
+  </si>
+  <si>
+    <t>VanderKooi</t>
   </si>
 </sst>
 </file>
@@ -1160,7 +1169,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{53695F79-F0CB-49F9-A1E9-F0A0A3F6EDBE}">
-  <dimension ref="A1:AQ82"/>
+  <dimension ref="A1:AQ85"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13.33203125" customWidth="1"/>
@@ -2671,81 +2680,27 @@
     </row>
     <row r="30" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>158</v>
-      </c>
-      <c r="E30" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="G30" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="H30" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="I30" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="L30" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="M30" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="Q30" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="R30" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="U30" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="X30" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="Y30" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="AC30" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="AD30" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="AE30" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="AF30" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="AL30" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="AM30" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="AP30" s="3" t="s">
-        <v>44</v>
+        <v>159</v>
       </c>
     </row>
     <row r="31" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>73</v>
-      </c>
-      <c r="C31" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="D31" s="3" t="s">
-        <v>44</v>
+        <v>158</v>
+      </c>
+      <c r="E31" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="G31" s="3" t="s">
+        <v>45</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="J31" s="3" t="s">
-        <v>45</v>
+        <v>45</v>
+      </c>
+      <c r="L31" s="3" t="s">
+        <v>44</v>
       </c>
       <c r="M31" s="3" t="s">
         <v>45</v>
@@ -2754,57 +2709,57 @@
         <v>44</v>
       </c>
       <c r="R31" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="V31" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="W31" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="U31" s="3" t="s">
         <v>44</v>
       </c>
       <c r="X31" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="AB31" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="Y31" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="AC31" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="AD31" s="2" t="s">
         <v>44</v>
       </c>
       <c r="AE31" s="3" t="s">
         <v>44</v>
       </c>
       <c r="AF31" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="AJ31" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="AK31" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AL31" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="AO31" s="3" t="s">
-        <v>45</v>
+      <c r="AM31" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="AP31" s="3" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="32" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>74</v>
-      </c>
-      <c r="B32" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="F32" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="G32" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="H32" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="I32" s="2" t="s">
         <v>44</v>
       </c>
       <c r="J32" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="K32" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="M32" s="3" t="s">
         <v>45</v>
@@ -2813,7 +2768,7 @@
         <v>44</v>
       </c>
       <c r="R32" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="V32" s="2" t="s">
         <v>44</v>
@@ -2821,11 +2776,11 @@
       <c r="W32" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="Z32" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="AA32" s="3" t="s">
-        <v>45</v>
+      <c r="X32" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="AB32" s="3" t="s">
+        <v>44</v>
       </c>
       <c r="AE32" s="3" t="s">
         <v>44</v>
@@ -2833,28 +2788,28 @@
       <c r="AF32" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="AH32" s="3" t="s">
-        <v>45</v>
+      <c r="AJ32" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="AK32" s="2" t="s">
+        <v>44</v>
       </c>
       <c r="AL32" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="AM32" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="AQ32" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="AO32" s="3" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="33" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>75</v>
-      </c>
-      <c r="C33" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="D33" s="3" t="s">
-        <v>45</v>
+        <v>74</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="F33" s="3" t="s">
+        <v>44</v>
       </c>
       <c r="G33" s="3" t="s">
         <v>44</v>
@@ -2863,362 +2818,362 @@
         <v>44</v>
       </c>
       <c r="K33" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="O33" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="P33" s="2" t="s">
-        <v>44</v>
+        <v>44</v>
+      </c>
+      <c r="M33" s="3" t="s">
+        <v>45</v>
       </c>
       <c r="Q33" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="U33" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="X33" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="R33" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="V33" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="W33" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z33" s="3" t="s">
         <v>44</v>
       </c>
       <c r="AA33" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="AB33" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AE33" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="AF33" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="AJ33" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="AK33" s="2" t="s">
-        <v>44</v>
+        <v>44</v>
+      </c>
+      <c r="AH33" s="3" t="s">
+        <v>45</v>
       </c>
       <c r="AL33" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="AM33" s="3" t="s">
         <v>45</v>
+      </c>
+      <c r="AQ33" s="2" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="34" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>76</v>
-      </c>
-      <c r="B34" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="E34" s="3" t="s">
-        <v>44</v>
+        <v>75</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="D34" s="3" t="s">
+        <v>45</v>
       </c>
       <c r="G34" s="3" t="s">
         <v>44</v>
       </c>
       <c r="J34" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="L34" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="M34" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="S34" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="T34" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="V34" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="W34" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="K34" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O34" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="P34" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q34" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="U34" s="3" t="s">
         <v>44</v>
       </c>
       <c r="X34" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="Y34" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
+      </c>
+      <c r="AA34" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="AB34" s="3" t="s">
+        <v>44</v>
       </c>
       <c r="AE34" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AF34" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="AI34" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="AN34" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="AP34" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="AQ34" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="AJ34" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="AK34" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="AL34" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="AM34" s="3" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="35" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>77</v>
+        <v>76</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>45</v>
       </c>
       <c r="E35" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="F35" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="H35" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="I35" s="2" t="s">
+      <c r="G35" s="3" t="s">
         <v>44</v>
       </c>
       <c r="J35" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="K35" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="Q35" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="R35" s="3" t="s">
-        <v>44</v>
+      <c r="L35" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="M35" s="3" t="s">
+        <v>45</v>
       </c>
       <c r="S35" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="AA35" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="AB35" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="AC35" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="AD35" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="AG35" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="AH35" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="AL35" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="AM35" s="3" t="s">
-        <v>45</v>
+      <c r="T35" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="V35" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="W35" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="X35" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y35" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="AE35" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="AF35" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="AI35" s="3" t="s">
+        <v>44</v>
       </c>
       <c r="AN35" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="AP35" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="AQ35" s="2" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="36" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>78</v>
-      </c>
-      <c r="C36" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="D36" s="3" t="s">
-        <v>44</v>
+        <v>77</v>
       </c>
       <c r="E36" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="M36" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="N36" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="O36" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="P36" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="T36" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="U36" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="X36" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="Y36" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="Z36" s="3" t="s">
-        <v>45</v>
+      <c r="F36" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="H36" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="I36" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="J36" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="K36" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q36" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="R36" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="S36" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="AA36" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="AB36" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="AC36" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="AD36" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="AG36" s="3" t="s">
+        <v>44</v>
       </c>
       <c r="AH36" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="AI36" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="AJ36" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="AK36" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="AO36" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="AP36" s="3" t="s">
-        <v>44</v>
+      <c r="AL36" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="AM36" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="AN36" s="3" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="37" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>79</v>
+        <v>78</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>44</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="G37" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="H37" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="I37" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="J37" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="L37" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="R37" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="E37" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="M37" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="N37" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O37" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="P37" s="2" t="s">
         <v>45</v>
       </c>
       <c r="T37" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="U37" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
+      </c>
+      <c r="X37" s="3" t="s">
+        <v>44</v>
       </c>
       <c r="Y37" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="AB37" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="AC37" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="AD37" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="AE37" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="AG37" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="AL37" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="AM37" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="AN37" s="3" t="s">
-        <v>45</v>
+      <c r="Z37" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="AH37" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="AI37" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="AJ37" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="AK37" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="AO37" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="AP37" s="3" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="38" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>80</v>
+        <v>79</v>
+      </c>
+      <c r="D38" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="G38" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="H38" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="I38" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="J38" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="L38" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="R38" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="T38" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="U38" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y38" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="AB38" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="AC38" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="AD38" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="AE38" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="AG38" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="AL38" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="AM38" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="AN38" s="3" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="39" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>81</v>
-      </c>
-      <c r="B39" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="C39" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="F39" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="M39" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="N39" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="O39" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="P39" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="S39" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="T39" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="AA39" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="AB39" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="AC39" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="AD39" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="AF39" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="AG39" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="AO39" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="AP39" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="AQ39" s="2" t="s">
-        <v>44</v>
+        <v>80</v>
       </c>
     </row>
     <row r="40" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>82</v>
+        <v>81</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>45</v>
       </c>
       <c r="C40" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="D40" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="G40" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="K40" s="3" t="s">
+      <c r="F40" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="M40" s="3" t="s">
         <v>44</v>
       </c>
       <c r="N40" s="3" t="s">
@@ -3236,51 +3191,87 @@
       <c r="T40" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="X40" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="Y40" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="Z40" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="AE40" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="AI40" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="AJ40" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="AK40" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="AN40" s="3" t="s">
-        <v>44</v>
+      <c r="AA40" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="AB40" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="AC40" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="AD40" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="AF40" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="AG40" s="3" t="s">
+        <v>45</v>
       </c>
       <c r="AO40" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="AP40" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="AQ40" s="2" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="41" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>83</v>
-      </c>
-      <c r="F41" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="M41" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="D41" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="G41" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="K41" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="N41" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="O41" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="P41" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="S41" s="3" t="s">
         <v>44</v>
       </c>
       <c r="T41" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="AA41" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="AH41" s="3" t="s">
+      <c r="X41" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="Y41" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="Z41" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="AE41" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="AI41" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="AJ41" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="AK41" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="AN41" s="3" t="s">
         <v>44</v>
       </c>
       <c r="AO41" s="3" t="s">
@@ -3289,116 +3280,80 @@
     </row>
     <row r="42" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>84</v>
-      </c>
-      <c r="C42" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="D42" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="G42" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="J42" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="K42" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="O42" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="P42" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="Q42" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="S42" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="Y42" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="F42" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="M42" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="T42" s="3" t="s">
         <v>44</v>
       </c>
       <c r="AA42" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="AB42" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="AE42" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="AF42" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="AJ42" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="AK42" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="AM42" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="AP42" s="3" t="s">
+      <c r="AH42" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="AO42" s="3" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="43" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="E43" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="H43" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="I43" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="L43" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="N43" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="D43" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="G43" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="J43" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="K43" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="O43" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="P43" s="2" t="s">
         <v>44</v>
       </c>
       <c r="Q43" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="T43" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="U43" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="X43" s="3" t="s">
-        <v>44</v>
+      <c r="S43" s="3" t="s">
+        <v>45</v>
       </c>
       <c r="Y43" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="AC43" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="AD43" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="AG43" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="AI43" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="AL43" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="AO43" s="3" t="s">
+      <c r="AA43" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="AB43" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="AE43" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="AF43" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="AJ43" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="AK43" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="AM43" s="3" t="s">
         <v>44</v>
       </c>
       <c r="AP43" s="3" t="s">
@@ -3407,104 +3362,104 @@
     </row>
     <row r="44" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
-        <v>86</v>
+        <v>85</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="H44" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="I44" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="L44" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="N44" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q44" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="T44" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="U44" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="X44" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="Y44" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="AC44" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="AD44" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="AG44" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="AI44" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="AL44" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="AO44" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="AP44" s="3" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="45" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
-        <v>87</v>
-      </c>
-      <c r="B45" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="E45" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="F45" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="L45" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="M45" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="N45" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="R45" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="U45" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="V45" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="W45" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="X45" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="AB45" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="AE45" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="AF45" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="AG45" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="AO45" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="AP45" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="AQ45" s="2" t="s">
-        <v>45</v>
+        <v>86</v>
       </c>
     </row>
     <row r="46" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
-        <v>88</v>
-      </c>
-      <c r="C46" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="D46" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="H46" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="I46" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E46" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="F46" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="L46" s="3" t="s">
         <v>44</v>
       </c>
       <c r="M46" s="3" t="s">
         <v>44</v>
       </c>
       <c r="N46" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="Q46" s="3" t="s">
         <v>44</v>
       </c>
       <c r="R46" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="U46" s="3" t="s">
         <v>44</v>
       </c>
       <c r="V46" s="2" t="s">
         <v>44</v>
       </c>
       <c r="W46" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="AA46" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="X46" s="3" t="s">
+        <v>45</v>
       </c>
       <c r="AB46" s="3" t="s">
         <v>44</v>
@@ -3515,84 +3470,84 @@
       <c r="AF46" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="AJ46" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="AK46" s="2" t="s">
+      <c r="AG46" s="3" t="s">
         <v>45</v>
       </c>
       <c r="AO46" s="3" t="s">
         <v>44</v>
       </c>
       <c r="AP46" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="AQ46" s="2" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="47" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
-        <v>89</v>
-      </c>
-      <c r="B47" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="E47" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="F47" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="L47" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="C47" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="D47" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="H47" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="I47" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="M47" s="3" t="s">
         <v>44</v>
       </c>
       <c r="N47" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="O47" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="P47" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="S47" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="T47" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="X47" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="Z47" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="AC47" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="AD47" s="2" t="s">
+      <c r="Q47" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="R47" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="V47" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="W47" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="AA47" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="AB47" s="3" t="s">
         <v>44</v>
       </c>
       <c r="AE47" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="AG47" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="AL47" s="3" t="s">
+      <c r="AF47" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="AJ47" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="AK47" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="AO47" s="3" t="s">
         <v>44</v>
       </c>
       <c r="AP47" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="AQ47" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="48" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
-        <v>90</v>
-      </c>
-      <c r="C48" s="3" t="s">
-        <v>44</v>
+        <v>89</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>45</v>
       </c>
       <c r="E48" s="3" t="s">
         <v>44</v>
@@ -3600,7 +3555,7 @@
       <c r="F48" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="K48" s="3" t="s">
+      <c r="L48" s="3" t="s">
         <v>44</v>
       </c>
       <c r="N48" s="3" t="s">
@@ -3613,57 +3568,57 @@
         <v>45</v>
       </c>
       <c r="S48" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="T48" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="X48" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="Y48" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="Z48" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="AH48" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="AI48" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="AJ48" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="AK48" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="AO48" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="AC48" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="AD48" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="AE48" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="AG48" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="AL48" s="3" t="s">
         <v>44</v>
       </c>
       <c r="AP48" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="AQ48" s="2" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="49" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
-        <v>91</v>
-      </c>
-      <c r="D49" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="C49" s="3" t="s">
         <v>44</v>
       </c>
       <c r="E49" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="G49" s="3" t="s">
+      <c r="F49" s="3" t="s">
         <v>44</v>
       </c>
       <c r="K49" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="N49" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="O49" s="2" t="s">
         <v>45</v>
@@ -3671,26 +3626,26 @@
       <c r="P49" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="Q49" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="U49" s="3" t="s">
-        <v>44</v>
+      <c r="S49" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="T49" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="X49" s="3" t="s">
+        <v>45</v>
       </c>
       <c r="Y49" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="Z49" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="AB49" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="AF49" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="AG49" s="3" t="s">
-        <v>45</v>
+        <v>45</v>
+      </c>
+      <c r="AH49" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="AI49" s="3" t="s">
+        <v>44</v>
       </c>
       <c r="AJ49" s="2" t="s">
         <v>44</v>
@@ -3698,400 +3653,400 @@
       <c r="AK49" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="AM49" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="AN49" s="3" t="s">
+      <c r="AO49" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="AP49" s="3" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="50" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
-        <v>92</v>
-      </c>
-      <c r="B50" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="V50" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="W50" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="AQ50" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="D50" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="E50" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="G50" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="K50" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="N50" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="O50" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="P50" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q50" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="U50" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="Y50" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z50" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="AB50" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="AF50" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="AG50" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="AJ50" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="AK50" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="AM50" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="AN50" s="3" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="51" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
-        <v>93</v>
-      </c>
-      <c r="C51" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="D51" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="E51" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="J51" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="K51" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="O51" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="P51" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="Q51" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="T51" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="X51" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="Y51" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="AB51" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="AH51" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="AI51" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="AJ51" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="AM51" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="AO51" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="AP51" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="V51" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="W51" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="AQ51" s="2" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="52" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
-        <v>94</v>
+        <v>93</v>
+      </c>
+      <c r="C52" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D52" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E52" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="J52" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="K52" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O52" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="P52" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q52" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="T52" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="X52" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="Y52" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="AB52" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="AH52" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="AI52" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="AJ52" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="AM52" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="AO52" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="AP52" s="3" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="53" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
-        <v>95</v>
-      </c>
-      <c r="B53" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="F53" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="G53" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="J53" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="L53" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="O53" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="P53" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="T53" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="U53" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="X53" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="Y53" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="AC53" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="AD53" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="AF53" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="AH53" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="AL53" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="AN53" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="AQ53" s="2" t="s">
-        <v>44</v>
+        <v>94</v>
       </c>
     </row>
     <row r="54" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
-        <v>96</v>
+        <v>95</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="F54" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="G54" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="J54" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="L54" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O54" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="P54" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="T54" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="U54" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="X54" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="Y54" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="AC54" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="AD54" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="AF54" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="AH54" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="AL54" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="AN54" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="AQ54" s="2" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="55" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
-        <v>97</v>
-      </c>
-      <c r="C55" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="D55" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="F55" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="J55" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="N55" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="O55" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="P55" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="S55" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="T55" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="X55" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="Y55" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="Z55" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="AG55" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="AI55" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="AJ55" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="AK55" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="AM55" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="AN55" s="3" t="s">
-        <v>45</v>
+        <v>96</v>
       </c>
     </row>
     <row r="56" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
-        <v>98</v>
+        <v>97</v>
+      </c>
+      <c r="C56" s="3" t="s">
+        <v>44</v>
       </c>
       <c r="D56" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="K56" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="R56" s="3" t="s">
+      <c r="F56" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="J56" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="N56" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="O56" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="P56" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="S56" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="T56" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="X56" s="3" t="s">
         <v>44</v>
       </c>
       <c r="Y56" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="AF56" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="Z56" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="AG56" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="AI56" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="AJ56" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="AK56" s="2" t="s">
         <v>44</v>
       </c>
       <c r="AM56" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="AN56" s="3" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="57" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
-        <v>99</v>
-      </c>
-      <c r="J57" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="U57" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="AL57" s="3" t="s">
-        <v>45</v>
+        <v>98</v>
+      </c>
+      <c r="D57" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="K57" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="R57" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="Y57" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="AF57" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="AM57" s="3" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="58" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
-        <v>100</v>
-      </c>
-      <c r="F58" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="G58" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="H58" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="I58" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="K58" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="L58" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="Q58" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="R58" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="S58" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="Z58" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="AB58" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="AC58" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="AD58" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="AG58" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="AH58" s="3" t="s">
-        <v>44</v>
+        <v>99</v>
+      </c>
+      <c r="J58" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="U58" s="3" t="s">
+        <v>45</v>
       </c>
       <c r="AL58" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="AM58" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="AP58" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="59" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
-        <v>101</v>
-      </c>
-      <c r="D59" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="E59" s="3" t="s">
-        <v>44</v>
+        <v>100</v>
       </c>
       <c r="F59" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="J59" s="3" t="s">
+      <c r="G59" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="H59" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="I59" s="2" t="s">
         <v>44</v>
       </c>
       <c r="K59" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="L59" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="T59" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="U59" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="V59" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="W59" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q59" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="R59" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="S59" s="3" t="s">
         <v>45</v>
       </c>
       <c r="Z59" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="AA59" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="AE59" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="AF59" s="3" t="s">
-        <v>44</v>
+      <c r="AB59" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="AC59" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="AD59" s="2" t="s">
+        <v>45</v>
       </c>
       <c r="AG59" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="AN59" s="3" t="s">
+      <c r="AH59" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="AL59" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="AM59" s="3" t="s">
         <v>44</v>
       </c>
       <c r="AP59" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="AQ59" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="60" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
-        <v>102</v>
-      </c>
-      <c r="B60" s="2" t="s">
-        <v>44</v>
+        <v>101</v>
       </c>
       <c r="D60" s="3" t="s">
         <v>44</v>
       </c>
+      <c r="E60" s="3" t="s">
+        <v>44</v>
+      </c>
       <c r="F60" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
+      </c>
+      <c r="J60" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="K60" s="3" t="s">
+        <v>44</v>
       </c>
       <c r="L60" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="M60" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="N60" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="R60" s="3" t="s">
-        <v>44</v>
-      </c>
       <c r="T60" s="3" t="s">
         <v>44</v>
       </c>
+      <c r="U60" s="3" t="s">
+        <v>45</v>
+      </c>
       <c r="V60" s="2" t="s">
         <v>45</v>
       </c>
@@ -4101,8 +4056,11 @@
       <c r="Z60" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="AB60" s="3" t="s">
-        <v>45</v>
+      <c r="AA60" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="AE60" s="3" t="s">
+        <v>44</v>
       </c>
       <c r="AF60" s="3" t="s">
         <v>44</v>
@@ -4110,366 +4068,360 @@
       <c r="AG60" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="AH60" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="AM60" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="AO60" s="3" t="s">
-        <v>44</v>
+      <c r="AN60" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="AP60" s="3" t="s">
+        <v>45</v>
       </c>
       <c r="AQ60" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="61" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
-        <v>103</v>
-      </c>
-      <c r="E61" s="3" t="s">
-        <v>44</v>
+        <v>102</v>
+      </c>
+      <c r="B61" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D61" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="F61" s="3" t="s">
+        <v>45</v>
       </c>
       <c r="L61" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="S61" s="3" t="s">
-        <v>44</v>
+      <c r="M61" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="N61" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="R61" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="T61" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="V61" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="W61" s="2" t="s">
+        <v>45</v>
       </c>
       <c r="Z61" s="3" t="s">
         <v>44</v>
       </c>
+      <c r="AB61" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="AF61" s="3" t="s">
+        <v>44</v>
+      </c>
       <c r="AG61" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="AN61" s="3" t="s">
+      <c r="AH61" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="AM61" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="AO61" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="AQ61" s="2" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="62" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
-        <v>104</v>
-      </c>
-      <c r="D62" s="3" t="s">
-        <v>44</v>
+        <v>103</v>
       </c>
       <c r="E62" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="H62" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="I62" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="M62" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="N62" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="Q62" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="R62" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="U62" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="Y62" s="3" t="s">
+      <c r="L62" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="S62" s="3" t="s">
         <v>44</v>
       </c>
       <c r="Z62" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="AC62" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="AD62" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="AH62" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="AI62" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="AL62" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="AO62" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="AP62" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="AG62" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="AN62" s="3" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="63" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
-        <v>105</v>
-      </c>
-      <c r="J63" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="D63" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="E63" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="H63" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="I63" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="M63" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="N63" s="3" t="s">
         <v>44</v>
       </c>
       <c r="Q63" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="R63" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="U63" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="Y63" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z63" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="AC63" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="AD63" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="AH63" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="AI63" s="3" t="s">
         <v>44</v>
       </c>
       <c r="AL63" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="AO63" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="AP63" s="3" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="64" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
-        <v>106</v>
-      </c>
-      <c r="B64" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="E64" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="F64" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="M64" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="N64" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="O64" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="P64" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="S64" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="T64" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="Y64" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="AB64" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="AC64" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="AD64" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="AE64" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="AG64" s="3" t="s">
-        <v>45</v>
+        <v>105</v>
+      </c>
+      <c r="J64" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q64" s="3" t="s">
+        <v>44</v>
       </c>
       <c r="AL64" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="AM64" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="AQ64" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="65" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="C65" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="E65" s="3" t="s">
+        <v>45</v>
       </c>
       <c r="F65" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="J65" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="K65" s="3" t="s">
-        <v>44</v>
-      </c>
       <c r="M65" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="R65" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="U65" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="V65" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="N65" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O65" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="P65" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="S65" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="T65" s="3" t="s">
         <v>45</v>
       </c>
       <c r="Y65" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="Z65" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="AA65" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="AB65" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="AC65" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="AD65" s="2" t="s">
         <v>45</v>
       </c>
       <c r="AE65" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AG65" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="AH65" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="AN65" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="AP65" s="3" t="s">
-        <v>44</v>
+      <c r="AL65" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="AM65" s="3" t="s">
+        <v>45</v>
       </c>
       <c r="AQ65" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="66" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
-        <v>108</v>
-      </c>
-      <c r="D66" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="B66" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C66" s="3" t="s">
         <v>44</v>
       </c>
       <c r="F66" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="H66" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="I66" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="L66" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="J66" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="K66" s="3" t="s">
         <v>44</v>
       </c>
       <c r="M66" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="Q66" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="S66" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="T66" s="3" t="s">
-        <v>44</v>
+      <c r="R66" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="U66" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="V66" s="2" t="s">
+        <v>45</v>
       </c>
       <c r="Y66" s="3" t="s">
         <v>44</v>
       </c>
+      <c r="Z66" s="3" t="s">
+        <v>45</v>
+      </c>
       <c r="AA66" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="AC66" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="AD66" s="2" t="s">
-        <v>45</v>
+        <v>45</v>
+      </c>
+      <c r="AE66" s="3" t="s">
+        <v>44</v>
       </c>
       <c r="AG66" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AH66" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="AL66" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AN66" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="AO66" s="3" t="s">
+      <c r="AP66" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="AQ66" s="2" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="67" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
-        <v>109</v>
-      </c>
-      <c r="B67" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="E67" s="3" t="s">
-        <v>45</v>
+        <v>108</v>
+      </c>
+      <c r="D67" s="3" t="s">
+        <v>44</v>
       </c>
       <c r="F67" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="J67" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="K67" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="N67" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="R67" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="U67" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="V67" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="W67" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="Z67" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="H67" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="I67" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="L67" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="M67" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q67" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="S67" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="T67" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="Y67" s="3" t="s">
         <v>44</v>
       </c>
       <c r="AA67" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="AE67" s="3" t="s">
-        <v>45</v>
+      <c r="AC67" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="AD67" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="AG67" s="3" t="s">
+        <v>44</v>
       </c>
       <c r="AH67" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="AI67" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="AM67" s="3" t="s">
-        <v>45</v>
+      <c r="AL67" s="3" t="s">
+        <v>44</v>
       </c>
       <c r="AN67" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="AQ67" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="AO67" s="3" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="68" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
-        <v>110</v>
-      </c>
-      <c r="D68" s="3" t="s">
-        <v>45</v>
+        <v>109</v>
+      </c>
+      <c r="B68" s="2" t="s">
+        <v>44</v>
       </c>
       <c r="E68" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="H68" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="I68" s="2" t="s">
-        <v>44</v>
+      <c r="F68" s="3" t="s">
+        <v>45</v>
       </c>
       <c r="J68" s="3" t="s">
         <v>44</v>
@@ -4477,69 +4429,72 @@
       <c r="K68" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="S68" s="3" t="s">
+      <c r="N68" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="R68" s="3" t="s">
         <v>44</v>
       </c>
       <c r="U68" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="V68" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="W68" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="X68" s="3" t="s">
-        <v>45</v>
+        <v>45</v>
+      </c>
+      <c r="Z68" s="3" t="s">
+        <v>44</v>
       </c>
       <c r="AA68" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="AG68" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="AE68" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="AH68" s="3" t="s">
         <v>44</v>
       </c>
       <c r="AI68" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="AJ68" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="AK68" s="2" t="s">
+      <c r="AM68" s="3" t="s">
         <v>45</v>
       </c>
       <c r="AN68" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="AO68" s="3" t="s">
-        <v>45</v>
+        <v>45</v>
+      </c>
+      <c r="AQ68" s="2" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="69" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
-        <v>111</v>
-      </c>
-      <c r="B69" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="F69" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="G69" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="D69" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E69" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="H69" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="I69" s="2" t="s">
         <v>44</v>
       </c>
       <c r="J69" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="L69" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="M69" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="Q69" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="R69" s="3" t="s">
+      <c r="K69" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="S69" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="U69" s="3" t="s">
         <v>44</v>
       </c>
       <c r="V69" s="2" t="s">
@@ -4552,303 +4507,285 @@
         <v>45</v>
       </c>
       <c r="AA69" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="AE69" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="AF69" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AG69" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="AL69" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="AM69" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="AQ69" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="AI69" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="AJ69" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="AK69" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="AN69" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="AO69" s="3" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="70" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
-        <v>112</v>
+        <v>111</v>
+      </c>
+      <c r="B70" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="F70" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="G70" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="J70" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="L70" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="M70" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q70" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="R70" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="V70" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="W70" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="X70" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA70" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="AE70" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="AF70" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="AG70" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="AL70" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="AM70" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="AQ70" s="2" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="71" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
-        <v>113</v>
-      </c>
-      <c r="F71" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="G71" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="H71" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="I71" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="K71" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="L71" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="S71" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="T71" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="U71" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="AA71" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="AB71" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="AC71" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="AD71" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="AG71" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="AH71" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="AL71" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="AM71" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="AO71" s="3" t="s">
-        <v>45</v>
+        <v>112</v>
       </c>
     </row>
     <row r="72" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
-        <v>157</v>
-      </c>
-      <c r="O72" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="P72" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="AI72" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="AJ72" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="F72" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="G72" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="H72" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="I72" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="K72" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="L72" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="S72" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="T72" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="U72" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA72" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="AB72" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="AC72" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="AD72" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="AG72" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="AH72" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="AL72" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="AM72" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="AO72" s="3" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="73" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
-        <v>114</v>
-      </c>
-      <c r="D73" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="E73" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="H73" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="I73" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="L73" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="M73" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="R73" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="T73" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="U73" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="Y73" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="Z73" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="AC73" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="AD73" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="AG73" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="AH73" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="AM73" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="AO73" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="AP73" s="3" t="s">
-        <v>44</v>
+        <v>157</v>
+      </c>
+      <c r="O73" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="P73" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="AI73" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="AJ73" s="2" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="74" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
-        <v>115</v>
-      </c>
-      <c r="C74" s="3" t="s">
-        <v>44</v>
+        <v>114</v>
       </c>
       <c r="D74" s="3" t="s">
         <v>44</v>
       </c>
+      <c r="E74" s="3" t="s">
+        <v>45</v>
+      </c>
       <c r="H74" s="2" t="s">
         <v>44</v>
       </c>
       <c r="I74" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="J74" s="3" t="s">
-        <v>45</v>
+        <v>45</v>
+      </c>
+      <c r="L74" s="3" t="s">
+        <v>44</v>
       </c>
       <c r="M74" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="Q74" s="3" t="s">
         <v>44</v>
       </c>
       <c r="R74" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="V74" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="W74" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="X74" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="AB74" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="AE74" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="AF74" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="AJ74" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="AK74" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="AL74" s="3" t="s">
-        <v>45</v>
+      <c r="T74" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="U74" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="Y74" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z74" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="AC74" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="AD74" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="AG74" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="AH74" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="AM74" s="3" t="s">
+        <v>44</v>
       </c>
       <c r="AO74" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
+      </c>
+      <c r="AP74" s="3" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="75" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
-        <v>116</v>
-      </c>
-      <c r="E75" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="M75" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="S75" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="AA75" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="AH75" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="AO75" s="3" t="s">
-        <v>44</v>
+        <v>160</v>
       </c>
     </row>
     <row r="76" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C76" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="G76" s="3" t="s">
-        <v>45</v>
+      <c r="D76" s="3" t="s">
+        <v>44</v>
       </c>
       <c r="H76" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="I76" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="J76" s="3" t="s">
         <v>45</v>
       </c>
       <c r="M76" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="N76" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q76" s="3" t="s">
         <v>44</v>
       </c>
       <c r="R76" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="S76" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="T76" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="Y76" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="AA76" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="AC76" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="AD76" s="2" t="s">
+      <c r="V76" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="W76" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="X76" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="AB76" s="3" t="s">
         <v>44</v>
       </c>
       <c r="AE76" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="AI76" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="AM76" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="AN76" s="3" t="s">
-        <v>44</v>
+        <v>44</v>
+      </c>
+      <c r="AF76" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="AJ76" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="AK76" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="AL76" s="3" t="s">
+        <v>45</v>
       </c>
       <c r="AO76" s="3" t="s">
         <v>45</v>
@@ -4856,259 +4793,346 @@
     </row>
     <row r="77" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
-        <v>118</v>
-      </c>
-      <c r="O77" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="P77" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="AJ77" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="AK77" s="2" t="s">
-        <v>45</v>
+        <v>116</v>
+      </c>
+      <c r="E77" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="M77" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="S77" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="AA77" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="AH77" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="AO77" s="3" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="78" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
-        <v>119</v>
+        <v>117</v>
+      </c>
+      <c r="C78" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="G78" s="3" t="s">
+        <v>45</v>
       </c>
       <c r="H78" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="I78" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="V78" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="W78" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="AJ78" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="AK78" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="M78" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="N78" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="R78" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="S78" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="T78" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y78" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="AA78" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="AC78" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="AD78" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="AE78" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="AI78" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="AM78" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="AN78" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="AO78" s="3" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="79" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
-        <v>120</v>
-      </c>
-      <c r="C79" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="E79" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="J79" s="3" t="s">
-        <v>44</v>
+        <v>118</v>
       </c>
       <c r="O79" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="Q79" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="S79" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="X79" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="Z79" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="AE79" s="3" t="s">
+      <c r="P79" s="2" t="s">
         <v>44</v>
       </c>
       <c r="AJ79" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="AL79" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="AN79" s="3" t="s">
-        <v>44</v>
+      <c r="AK79" s="2" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="80" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
-        <v>121</v>
-      </c>
-      <c r="C80" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="F80" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="G80" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="K80" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="L80" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="O80" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="P80" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="Q80" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="U80" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="X80" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="AA80" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="AB80" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="AH80" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="AI80" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="H80" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="I80" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="V80" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="W80" s="2" t="s">
         <v>45</v>
       </c>
       <c r="AJ80" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="AK80" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="AN80" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="AO80" s="3" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="81" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
-        <v>122</v>
-      </c>
-      <c r="B81" s="2" t="s">
-        <v>44</v>
+        <v>120</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="D81" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
+      </c>
+      <c r="E81" s="3" t="s">
+        <v>44</v>
       </c>
       <c r="J81" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="K81" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="L81" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="T81" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="U81" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="V81" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="W81" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="AA81" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="AB81" s="3" t="s">
+      <c r="O81" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q81" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="S81" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="X81" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z81" s="3" t="s">
         <v>44</v>
       </c>
       <c r="AE81" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="AF81" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="AG81" s="3" t="s">
-        <v>45</v>
+      <c r="AJ81" s="2" t="s">
+        <v>44</v>
       </c>
       <c r="AL81" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="AM81" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="AQ81" s="2" t="s">
+      <c r="AN81" s="3" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="82" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
+        <v>121</v>
+      </c>
+      <c r="C82" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="F82" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="G82" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="K82" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="L82" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O82" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="P82" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q82" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="U82" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="X82" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="AA82" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="AB82" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="AH82" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="AI82" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="AJ82" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="AK82" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="AN82" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="AO82" s="3" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="83" spans="1:43" x14ac:dyDescent="0.2">
+      <c r="A83" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="84" spans="1:43" x14ac:dyDescent="0.2">
+      <c r="A84" t="s">
+        <v>122</v>
+      </c>
+      <c r="B84" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C84" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="D84" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="J84" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="K84" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="L84" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="T84" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="U84" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="V84" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="W84" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA84" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="AB84" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="AE84" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="AF84" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="AG84" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="AL84" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="AM84" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="AQ84" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="85" spans="1:43" x14ac:dyDescent="0.2">
+      <c r="A85" t="s">
         <v>123</v>
       </c>
-      <c r="C82" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="G82" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="H82" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="K82" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="L82" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="N82" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="Q82" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="R82" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="T82" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="X82" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="Y82" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="AC82" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="AD82" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="AE82" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="AF82" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="AL82" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="AM82" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="AN82" s="3" t="s">
+      <c r="C85" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="G85" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="H85" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="K85" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="L85" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="N85" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q85" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="R85" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="T85" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="X85" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="Y85" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="AC85" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="AD85" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="AE85" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="AF85" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="AL85" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="AM85" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="AN85" s="3" t="s">
         <v>45</v>
       </c>
     </row>
@@ -6225,23 +6249,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_Flow_SignoffStatus xmlns="3ae64878-e7bb-4c65-a932-4cdc61fbe63f" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009F702E5FD63918449A87815BC57997B4" ma:contentTypeVersion="7" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="f366023269454ced43510f73883a6d91">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="3ae64878-e7bb-4c65-a932-4cdc61fbe63f" xmlns:ns3="b0d30a24-05e2-4154-8fed-e579ddd987b0" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="dd01e2e1f35a8420c36650a8355a0ef6" ns2:_="" ns3:_="">
     <xsd:import namespace="3ae64878-e7bb-4c65-a932-4cdc61fbe63f"/>
@@ -6424,25 +6431,24 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9EFFDED6-61B9-426A-8C57-4EB4CD0F4E95}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_Flow_SignoffStatus xmlns="3ae64878-e7bb-4c65-a932-4cdc61fbe63f" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4ED2462D-4DC3-4D8C-9537-7DD0B7423608}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="3ae64878-e7bb-4c65-a932-4cdc61fbe63f"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2DEFF9ED-23D7-4EA5-99B7-575064A65984}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -6459,4 +6465,22 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4ED2462D-4DC3-4D8C-9537-7DD0B7423608}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="3ae64878-e7bb-4c65-a932-4cdc61fbe63f"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9EFFDED6-61B9-426A-8C57-4EB4CD0F4E95}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/upload files/Tracks.xlsx
+++ b/upload files/Tracks.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10621"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10810"/>
   <workbookPr updateLinks="always"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/aaronbell/Desktop/Git Repo Clone/CrewOps360/upload files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1C492AC-F23B-F442-8C1B-FC63F440369F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BAAD01C1-DE29-B942-B0EF-F98169761694}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="680" windowWidth="29040" windowHeight="17240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="680" windowWidth="29040" windowHeight="17240" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="3" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1529" uniqueCount="162">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1515" uniqueCount="161">
   <si>
     <t>STAFF NAME</t>
   </si>
@@ -414,9 +414,6 @@
     <t>Chatigny</t>
   </si>
   <si>
-    <t>Deptula</t>
-  </si>
-  <si>
     <t>DiCredico</t>
   </si>
   <si>
@@ -459,9 +456,6 @@
     <t>Tonelli</t>
   </si>
   <si>
-    <t>Turner</t>
-  </si>
-  <si>
     <t>Sun</t>
   </si>
   <si>
@@ -495,9 +489,6 @@
     <t>NP</t>
   </si>
   <si>
-    <t>FW</t>
-  </si>
-  <si>
     <t>SIM</t>
   </si>
   <si>
@@ -523,13 +514,19 @@
   </si>
   <si>
     <t>VanderKooi</t>
+  </si>
+  <si>
+    <t>Tavernelli</t>
+  </si>
+  <si>
+    <t>GR2</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -550,14 +547,8 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -594,8 +585,14 @@
         <bgColor rgb="FF000000"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBDD7EE"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="15">
+  <borders count="14">
     <border>
       <left/>
       <right/>
@@ -614,26 +611,6 @@
         <color rgb="FF000000"/>
       </top>
       <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FF000000"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FF000000"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="medium">
         <color rgb="FF000000"/>
       </bottom>
       <diagonal/>
@@ -687,48 +664,12 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
       <right/>
       <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color rgb="FF000000"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top/>
-      <bottom style="medium">
+      <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
       <diagonal/>
@@ -738,21 +679,90 @@
         <color rgb="FF000000"/>
       </left>
       <right/>
-      <top/>
-      <bottom style="medium">
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right style="medium">
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
         <color rgb="FF000000"/>
       </right>
       <top/>
-      <bottom style="medium">
+      <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
       <diagonal/>
     </border>
   </borders>
@@ -777,56 +787,56 @@
     <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2680,12 +2690,12 @@
     </row>
     <row r="30" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
     </row>
     <row r="31" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="E31" s="3" t="s">
         <v>44</v>
@@ -4653,7 +4663,7 @@
     </row>
     <row r="73" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="O73" s="2" t="s">
         <v>44</v>
@@ -4729,7 +4739,7 @@
     </row>
     <row r="75" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
     </row>
     <row r="76" spans="1:43" x14ac:dyDescent="0.2">
@@ -5015,7 +5025,7 @@
     </row>
     <row r="83" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
     </row>
     <row r="84" spans="1:43" x14ac:dyDescent="0.2">
@@ -5143,1105 +5153,1046 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8A47ABB5-6B6D-0047-BC0D-8743FEF36D8D}">
-  <dimension ref="A1:AC18"/>
+  <dimension ref="A1:AC17"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:29" ht="16" x14ac:dyDescent="0.2">
       <c r="B1" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="D1" s="8" t="s">
         <v>141</v>
       </c>
-      <c r="C1" s="8" t="s">
+      <c r="E1" s="8" t="s">
         <v>142</v>
       </c>
-      <c r="D1" s="8" t="s">
+      <c r="F1" s="8" t="s">
         <v>143</v>
       </c>
-      <c r="E1" s="8" t="s">
+      <c r="G1" s="8" t="s">
         <v>144</v>
       </c>
-      <c r="F1" s="8" t="s">
+      <c r="H1" s="9" t="s">
         <v>145</v>
       </c>
-      <c r="G1" s="8" t="s">
-        <v>146</v>
-      </c>
-      <c r="H1" s="9" t="s">
-        <v>147</v>
-      </c>
       <c r="I1" s="10" t="s">
+        <v>139</v>
+      </c>
+      <c r="J1" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="K1" s="8" t="s">
         <v>141</v>
       </c>
-      <c r="J1" s="8" t="s">
+      <c r="L1" s="8" t="s">
         <v>142</v>
       </c>
-      <c r="K1" s="8" t="s">
+      <c r="M1" s="8" t="s">
         <v>143</v>
       </c>
-      <c r="L1" s="8" t="s">
+      <c r="N1" s="8" t="s">
         <v>144</v>
       </c>
-      <c r="M1" s="8" t="s">
+      <c r="O1" s="11" t="s">
         <v>145</v>
       </c>
-      <c r="N1" s="8" t="s">
-        <v>146</v>
-      </c>
-      <c r="O1" s="11" t="s">
-        <v>147</v>
-      </c>
       <c r="P1" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="Q1" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="R1" s="8" t="s">
         <v>141</v>
       </c>
-      <c r="Q1" s="8" t="s">
+      <c r="S1" s="8" t="s">
         <v>142</v>
       </c>
-      <c r="R1" s="8" t="s">
+      <c r="T1" s="8" t="s">
         <v>143</v>
       </c>
-      <c r="S1" s="8" t="s">
+      <c r="U1" s="8" t="s">
         <v>144</v>
       </c>
-      <c r="T1" s="8" t="s">
+      <c r="V1" s="9" t="s">
         <v>145</v>
       </c>
-      <c r="U1" s="8" t="s">
-        <v>146</v>
-      </c>
-      <c r="V1" s="9" t="s">
-        <v>147</v>
-      </c>
       <c r="W1" s="10" t="s">
+        <v>139</v>
+      </c>
+      <c r="X1" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="Y1" s="8" t="s">
         <v>141</v>
       </c>
-      <c r="X1" s="8" t="s">
+      <c r="Z1" s="8" t="s">
         <v>142</v>
       </c>
-      <c r="Y1" s="8" t="s">
+      <c r="AA1" s="8" t="s">
         <v>143</v>
       </c>
-      <c r="Z1" s="8" t="s">
+      <c r="AB1" s="8" t="s">
         <v>144</v>
       </c>
-      <c r="AA1" s="8" t="s">
+      <c r="AC1" s="11" t="s">
         <v>145</v>
       </c>
-      <c r="AB1" s="8" t="s">
-        <v>146</v>
-      </c>
-      <c r="AC1" s="11" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="2" spans="1:29" x14ac:dyDescent="0.2">
+    </row>
+    <row r="2" spans="1:29" ht="16" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>124</v>
       </c>
       <c r="B2" s="12"/>
       <c r="C2" s="13" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="D2" s="13" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="E2" s="13"/>
       <c r="F2" s="13"/>
       <c r="G2" s="13" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="H2" s="14" t="s">
-        <v>148</v>
-      </c>
-      <c r="I2" s="15" t="s">
-        <v>148</v>
+        <v>146</v>
+      </c>
+      <c r="I2" s="14" t="s">
+        <v>146</v>
       </c>
       <c r="J2" s="13"/>
       <c r="K2" s="13"/>
       <c r="L2" s="13" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="M2" s="13" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="N2" s="13"/>
-      <c r="O2" s="16"/>
+      <c r="O2" s="15"/>
       <c r="P2" s="12"/>
       <c r="Q2" s="13" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="R2" s="13" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="S2" s="13"/>
       <c r="T2" s="13"/>
       <c r="U2" s="13" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="V2" s="14" t="s">
-        <v>149</v>
-      </c>
-      <c r="W2" s="15" t="s">
-        <v>149</v>
+        <v>147</v>
+      </c>
+      <c r="W2" s="14" t="s">
+        <v>147</v>
       </c>
       <c r="X2" s="13"/>
       <c r="Y2" s="13"/>
       <c r="Z2" s="13" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="AA2" s="13" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="AB2" s="13"/>
-      <c r="AC2" s="17"/>
-    </row>
-    <row r="3" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AC2" s="15"/>
+    </row>
+    <row r="3" spans="1:29" ht="16" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>125</v>
       </c>
-      <c r="B3" s="12"/>
-      <c r="C3" s="13"/>
-      <c r="D3" s="13"/>
-      <c r="E3" s="13"/>
-      <c r="F3" s="13"/>
-      <c r="G3" s="13"/>
-      <c r="H3" s="14"/>
-      <c r="I3" s="15"/>
-      <c r="J3" s="13"/>
-      <c r="K3" s="13"/>
-      <c r="L3" s="13"/>
-      <c r="M3" s="13"/>
-      <c r="N3" s="13"/>
-      <c r="O3" s="16"/>
-      <c r="P3" s="12"/>
-      <c r="Q3" s="13"/>
-      <c r="R3" s="13"/>
-      <c r="S3" s="13"/>
-      <c r="T3" s="13"/>
-      <c r="U3" s="13"/>
-      <c r="V3" s="14"/>
-      <c r="W3" s="15"/>
-      <c r="X3" s="13"/>
-      <c r="Y3" s="13"/>
-      <c r="Z3" s="13"/>
-      <c r="AA3" s="13"/>
-      <c r="AB3" s="13"/>
-      <c r="AC3" s="17"/>
-    </row>
-    <row r="4" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="B3" s="16"/>
+      <c r="C3" s="17"/>
+      <c r="D3" s="17"/>
+      <c r="E3" s="17"/>
+      <c r="F3" s="17"/>
+      <c r="G3" s="17"/>
+      <c r="H3" s="18"/>
+      <c r="I3" s="18"/>
+      <c r="J3" s="17"/>
+      <c r="K3" s="17"/>
+      <c r="L3" s="17"/>
+      <c r="M3" s="17"/>
+      <c r="N3" s="17"/>
+      <c r="O3" s="19"/>
+      <c r="P3" s="16"/>
+      <c r="Q3" s="17"/>
+      <c r="R3" s="17"/>
+      <c r="S3" s="17"/>
+      <c r="T3" s="17"/>
+      <c r="U3" s="17"/>
+      <c r="V3" s="18"/>
+      <c r="W3" s="18"/>
+      <c r="X3" s="17"/>
+      <c r="Y3" s="17"/>
+      <c r="Z3" s="17"/>
+      <c r="AA3" s="17"/>
+      <c r="AB3" s="17"/>
+      <c r="AC3" s="19"/>
+    </row>
+    <row r="4" spans="1:29" ht="16" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>126</v>
       </c>
-      <c r="B4" s="12" t="s">
-        <v>148</v>
-      </c>
-      <c r="C4" s="13"/>
-      <c r="D4" s="13"/>
-      <c r="E4" s="13" t="s">
-        <v>148</v>
-      </c>
-      <c r="F4" s="13" t="s">
-        <v>148</v>
-      </c>
-      <c r="G4" s="13"/>
-      <c r="H4" s="14"/>
-      <c r="I4" s="15"/>
-      <c r="J4" s="13" t="s">
-        <v>148</v>
-      </c>
-      <c r="K4" s="13" t="s">
-        <v>148</v>
-      </c>
-      <c r="L4" s="13"/>
-      <c r="M4" s="13"/>
-      <c r="N4" s="13" t="s">
-        <v>149</v>
-      </c>
-      <c r="O4" s="16" t="s">
-        <v>149</v>
-      </c>
-      <c r="P4" s="12" t="s">
-        <v>149</v>
-      </c>
-      <c r="Q4" s="13"/>
-      <c r="R4" s="13"/>
-      <c r="S4" s="13" t="s">
-        <v>149</v>
-      </c>
-      <c r="T4" s="13" t="s">
-        <v>149</v>
-      </c>
-      <c r="U4" s="13"/>
-      <c r="V4" s="14"/>
-      <c r="W4" s="15"/>
-      <c r="X4" s="13" t="s">
-        <v>149</v>
-      </c>
-      <c r="Y4" s="13" t="s">
-        <v>149</v>
-      </c>
-      <c r="Z4" s="13"/>
-      <c r="AA4" s="13"/>
-      <c r="AB4" s="13" t="s">
-        <v>148</v>
-      </c>
-      <c r="AC4" s="17" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="5" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="B4" s="16" t="s">
+        <v>147</v>
+      </c>
+      <c r="C4" s="17"/>
+      <c r="D4" s="17"/>
+      <c r="E4" s="17" t="s">
+        <v>147</v>
+      </c>
+      <c r="F4" s="17" t="s">
+        <v>147</v>
+      </c>
+      <c r="G4" s="17"/>
+      <c r="H4" s="18"/>
+      <c r="I4" s="18"/>
+      <c r="J4" s="17" t="s">
+        <v>147</v>
+      </c>
+      <c r="K4" s="17" t="s">
+        <v>147</v>
+      </c>
+      <c r="L4" s="17"/>
+      <c r="M4" s="17"/>
+      <c r="N4" s="17" t="s">
+        <v>146</v>
+      </c>
+      <c r="O4" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="P4" s="16" t="s">
+        <v>146</v>
+      </c>
+      <c r="Q4" s="17"/>
+      <c r="R4" s="17"/>
+      <c r="S4" s="17" t="s">
+        <v>146</v>
+      </c>
+      <c r="T4" s="17" t="s">
+        <v>146</v>
+      </c>
+      <c r="U4" s="17"/>
+      <c r="V4" s="18"/>
+      <c r="W4" s="18"/>
+      <c r="X4" s="17" t="s">
+        <v>146</v>
+      </c>
+      <c r="Y4" s="17" t="s">
+        <v>146</v>
+      </c>
+      <c r="Z4" s="17"/>
+      <c r="AA4" s="17"/>
+      <c r="AB4" s="17" t="s">
+        <v>147</v>
+      </c>
+      <c r="AC4" s="19" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="5" spans="1:29" ht="16" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>127</v>
       </c>
-      <c r="B5" s="12" t="s">
-        <v>149</v>
-      </c>
-      <c r="C5" s="13"/>
-      <c r="D5" s="13"/>
-      <c r="E5" s="13" t="s">
-        <v>149</v>
-      </c>
-      <c r="F5" s="13" t="s">
-        <v>149</v>
-      </c>
-      <c r="G5" s="13"/>
-      <c r="H5" s="14"/>
-      <c r="I5" s="15"/>
-      <c r="J5" s="13" t="s">
-        <v>149</v>
-      </c>
-      <c r="K5" s="13" t="s">
-        <v>149</v>
-      </c>
-      <c r="L5" s="13"/>
-      <c r="M5" s="13"/>
-      <c r="N5" s="13" t="s">
+      <c r="B5" s="16"/>
+      <c r="C5" s="17" t="s">
         <v>148</v>
       </c>
-      <c r="O5" s="16" t="s">
+      <c r="D5" s="17" t="s">
         <v>148</v>
       </c>
-      <c r="P5" s="12" t="s">
+      <c r="E5" s="17"/>
+      <c r="F5" s="17"/>
+      <c r="G5" s="17" t="s">
         <v>148</v>
       </c>
-      <c r="Q5" s="13"/>
-      <c r="R5" s="13"/>
-      <c r="S5" s="13" t="s">
+      <c r="H5" s="18" t="s">
         <v>148</v>
       </c>
-      <c r="T5" s="13" t="s">
+      <c r="I5" s="18" t="s">
         <v>148</v>
       </c>
-      <c r="U5" s="13"/>
-      <c r="V5" s="14"/>
-      <c r="W5" s="15"/>
-      <c r="X5" s="13" t="s">
+      <c r="J5" s="17"/>
+      <c r="K5" s="17"/>
+      <c r="L5" s="17" t="s">
         <v>148</v>
       </c>
-      <c r="Y5" s="13" t="s">
+      <c r="M5" s="17" t="s">
         <v>148</v>
       </c>
-      <c r="Z5" s="13"/>
-      <c r="AA5" s="13"/>
-      <c r="AB5" s="13" t="s">
-        <v>149</v>
-      </c>
-      <c r="AC5" s="17" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="6" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="N5" s="17"/>
+      <c r="O5" s="19"/>
+      <c r="P5" s="16"/>
+      <c r="Q5" s="17" t="s">
+        <v>148</v>
+      </c>
+      <c r="R5" s="17" t="s">
+        <v>148</v>
+      </c>
+      <c r="S5" s="17"/>
+      <c r="T5" s="17"/>
+      <c r="U5" s="17" t="s">
+        <v>148</v>
+      </c>
+      <c r="V5" s="18" t="s">
+        <v>148</v>
+      </c>
+      <c r="W5" s="18" t="s">
+        <v>148</v>
+      </c>
+      <c r="X5" s="17"/>
+      <c r="Y5" s="17"/>
+      <c r="Z5" s="17" t="s">
+        <v>148</v>
+      </c>
+      <c r="AA5" s="17" t="s">
+        <v>148</v>
+      </c>
+      <c r="AB5" s="17"/>
+      <c r="AC5" s="19"/>
+    </row>
+    <row r="6" spans="1:29" ht="16" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>128</v>
       </c>
-      <c r="B6" s="12"/>
-      <c r="C6" s="13" t="s">
-        <v>150</v>
-      </c>
-      <c r="D6" s="13" t="s">
-        <v>150</v>
-      </c>
-      <c r="E6" s="13"/>
-      <c r="F6" s="13"/>
-      <c r="G6" s="13" t="s">
-        <v>150</v>
-      </c>
-      <c r="H6" s="14" t="s">
-        <v>150</v>
-      </c>
-      <c r="I6" s="15" t="s">
-        <v>150</v>
-      </c>
-      <c r="J6" s="13"/>
-      <c r="K6" s="13"/>
-      <c r="L6" s="13" t="s">
-        <v>151</v>
-      </c>
-      <c r="M6" s="13" t="s">
-        <v>151</v>
-      </c>
-      <c r="N6" s="13"/>
-      <c r="O6" s="16"/>
-      <c r="P6" s="12"/>
-      <c r="Q6" s="13"/>
-      <c r="R6" s="13"/>
-      <c r="S6" s="13" t="s">
-        <v>152</v>
-      </c>
-      <c r="T6" s="13" t="s">
-        <v>152</v>
-      </c>
-      <c r="U6" s="13"/>
-      <c r="V6" s="14"/>
-      <c r="W6" s="15"/>
-      <c r="X6" s="13" t="s">
-        <v>152</v>
-      </c>
-      <c r="Y6" s="13" t="s">
-        <v>152</v>
-      </c>
-      <c r="Z6" s="13"/>
-      <c r="AA6" s="13"/>
-      <c r="AB6" s="13" t="s">
-        <v>152</v>
-      </c>
-      <c r="AC6" s="17" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="7" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="B6" s="16"/>
+      <c r="C6" s="17" t="s">
+        <v>147</v>
+      </c>
+      <c r="D6" s="17" t="s">
+        <v>147</v>
+      </c>
+      <c r="E6" s="17"/>
+      <c r="F6" s="17"/>
+      <c r="G6" s="17" t="s">
+        <v>147</v>
+      </c>
+      <c r="H6" s="18" t="s">
+        <v>147</v>
+      </c>
+      <c r="I6" s="18" t="s">
+        <v>147</v>
+      </c>
+      <c r="J6" s="17"/>
+      <c r="K6" s="17"/>
+      <c r="L6" s="17" t="s">
+        <v>146</v>
+      </c>
+      <c r="M6" s="17" t="s">
+        <v>146</v>
+      </c>
+      <c r="N6" s="17"/>
+      <c r="O6" s="19"/>
+      <c r="P6" s="16"/>
+      <c r="Q6" s="17" t="s">
+        <v>146</v>
+      </c>
+      <c r="R6" s="17" t="s">
+        <v>146</v>
+      </c>
+      <c r="S6" s="17"/>
+      <c r="T6" s="17"/>
+      <c r="U6" s="17" t="s">
+        <v>146</v>
+      </c>
+      <c r="V6" s="18" t="s">
+        <v>146</v>
+      </c>
+      <c r="W6" s="18" t="s">
+        <v>146</v>
+      </c>
+      <c r="X6" s="17"/>
+      <c r="Y6" s="17"/>
+      <c r="Z6" s="17" t="s">
+        <v>147</v>
+      </c>
+      <c r="AA6" s="17" t="s">
+        <v>147</v>
+      </c>
+      <c r="AB6" s="17"/>
+      <c r="AC6" s="19"/>
+    </row>
+    <row r="7" spans="1:29" ht="16" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>129</v>
       </c>
-      <c r="B7" s="12"/>
-      <c r="C7" s="13" t="s">
-        <v>149</v>
-      </c>
-      <c r="D7" s="13" t="s">
-        <v>149</v>
-      </c>
-      <c r="E7" s="13"/>
-      <c r="F7" s="13"/>
-      <c r="G7" s="13" t="s">
-        <v>149</v>
-      </c>
-      <c r="H7" s="14" t="s">
-        <v>149</v>
-      </c>
-      <c r="I7" s="15" t="s">
-        <v>149</v>
-      </c>
-      <c r="J7" s="13"/>
-      <c r="K7" s="13"/>
-      <c r="L7" s="13" t="s">
-        <v>148</v>
-      </c>
-      <c r="M7" s="13" t="s">
-        <v>148</v>
-      </c>
-      <c r="N7" s="13"/>
-      <c r="O7" s="16"/>
-      <c r="P7" s="12"/>
-      <c r="Q7" s="13" t="s">
-        <v>148</v>
-      </c>
-      <c r="R7" s="13" t="s">
-        <v>148</v>
-      </c>
-      <c r="S7" s="13"/>
-      <c r="T7" s="13"/>
-      <c r="U7" s="13" t="s">
-        <v>148</v>
-      </c>
-      <c r="V7" s="14" t="s">
-        <v>148</v>
-      </c>
-      <c r="W7" s="15" t="s">
-        <v>148</v>
-      </c>
-      <c r="X7" s="13"/>
-      <c r="Y7" s="13"/>
-      <c r="Z7" s="13" t="s">
-        <v>149</v>
-      </c>
-      <c r="AA7" s="13" t="s">
-        <v>149</v>
-      </c>
-      <c r="AB7" s="13"/>
-      <c r="AC7" s="17"/>
-    </row>
-    <row r="8" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="B7" s="16"/>
+      <c r="C7" s="17"/>
+      <c r="D7" s="17" t="s">
+        <v>150</v>
+      </c>
+      <c r="E7" s="17" t="s">
+        <v>150</v>
+      </c>
+      <c r="F7" s="17"/>
+      <c r="G7" s="17" t="s">
+        <v>160</v>
+      </c>
+      <c r="H7" s="18" t="s">
+        <v>160</v>
+      </c>
+      <c r="I7" s="18" t="s">
+        <v>160</v>
+      </c>
+      <c r="J7" s="17"/>
+      <c r="K7" s="17" t="s">
+        <v>150</v>
+      </c>
+      <c r="L7" s="17" t="s">
+        <v>150</v>
+      </c>
+      <c r="M7" s="17" t="s">
+        <v>160</v>
+      </c>
+      <c r="N7" s="17"/>
+      <c r="O7" s="19"/>
+      <c r="P7" s="16"/>
+      <c r="Q7" s="17"/>
+      <c r="R7" s="17" t="s">
+        <v>150</v>
+      </c>
+      <c r="S7" s="17" t="s">
+        <v>150</v>
+      </c>
+      <c r="T7" s="17"/>
+      <c r="U7" s="17" t="s">
+        <v>160</v>
+      </c>
+      <c r="V7" s="18" t="s">
+        <v>160</v>
+      </c>
+      <c r="W7" s="18" t="s">
+        <v>160</v>
+      </c>
+      <c r="X7" s="17"/>
+      <c r="Y7" s="17" t="s">
+        <v>150</v>
+      </c>
+      <c r="Z7" s="17" t="s">
+        <v>150</v>
+      </c>
+      <c r="AA7" s="17" t="s">
+        <v>160</v>
+      </c>
+      <c r="AB7" s="17"/>
+      <c r="AC7" s="19"/>
+    </row>
+    <row r="8" spans="1:29" ht="16" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>130</v>
       </c>
-      <c r="B8" s="12"/>
-      <c r="C8" s="13"/>
-      <c r="D8" s="13" t="s">
-        <v>153</v>
-      </c>
-      <c r="E8" s="13" t="s">
-        <v>153</v>
-      </c>
-      <c r="F8" s="13"/>
-      <c r="G8" s="13" t="s">
-        <v>150</v>
-      </c>
-      <c r="H8" s="14" t="s">
-        <v>150</v>
-      </c>
-      <c r="I8" s="15" t="s">
-        <v>150</v>
-      </c>
-      <c r="J8" s="13"/>
-      <c r="K8" s="13" t="s">
-        <v>153</v>
-      </c>
-      <c r="L8" s="13" t="s">
-        <v>153</v>
-      </c>
-      <c r="M8" s="13" t="s">
+      <c r="B8" s="16"/>
+      <c r="C8" s="17" t="s">
         <v>151</v>
       </c>
-      <c r="N8" s="13"/>
-      <c r="O8" s="16"/>
-      <c r="P8" s="12"/>
-      <c r="Q8" s="13"/>
-      <c r="R8" s="13" t="s">
-        <v>153</v>
-      </c>
-      <c r="S8" s="13" t="s">
-        <v>153</v>
-      </c>
-      <c r="T8" s="13"/>
-      <c r="U8" s="13" t="s">
+      <c r="D8" s="17" t="s">
         <v>151</v>
       </c>
-      <c r="V8" s="14" t="s">
+      <c r="E8" s="17"/>
+      <c r="F8" s="17"/>
+      <c r="G8" s="17" t="s">
         <v>151</v>
       </c>
-      <c r="W8" s="15" t="s">
+      <c r="H8" s="18" t="s">
         <v>151</v>
       </c>
-      <c r="X8" s="13"/>
-      <c r="Y8" s="13" t="s">
-        <v>153</v>
-      </c>
-      <c r="Z8" s="13" t="s">
-        <v>153</v>
-      </c>
-      <c r="AA8" s="13" t="s">
-        <v>150</v>
-      </c>
-      <c r="AB8" s="13"/>
-      <c r="AC8" s="17"/>
-    </row>
-    <row r="9" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="I8" s="18" t="s">
+        <v>151</v>
+      </c>
+      <c r="J8" s="17"/>
+      <c r="K8" s="17"/>
+      <c r="L8" s="17" t="s">
+        <v>152</v>
+      </c>
+      <c r="M8" s="17" t="s">
+        <v>152</v>
+      </c>
+      <c r="N8" s="17"/>
+      <c r="O8" s="19"/>
+      <c r="P8" s="16"/>
+      <c r="Q8" s="17" t="s">
+        <v>152</v>
+      </c>
+      <c r="R8" s="17" t="s">
+        <v>152</v>
+      </c>
+      <c r="S8" s="17"/>
+      <c r="T8" s="17"/>
+      <c r="U8" s="17" t="s">
+        <v>152</v>
+      </c>
+      <c r="V8" s="18" t="s">
+        <v>152</v>
+      </c>
+      <c r="W8" s="18" t="s">
+        <v>152</v>
+      </c>
+      <c r="X8" s="17"/>
+      <c r="Y8" s="17"/>
+      <c r="Z8" s="17" t="s">
+        <v>151</v>
+      </c>
+      <c r="AA8" s="17" t="s">
+        <v>151</v>
+      </c>
+      <c r="AB8" s="17"/>
+      <c r="AC8" s="19"/>
+    </row>
+    <row r="9" spans="1:29" ht="16" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>131</v>
       </c>
-      <c r="B9" s="12"/>
-      <c r="C9" s="13" t="s">
-        <v>154</v>
-      </c>
-      <c r="D9" s="13" t="s">
-        <v>154</v>
-      </c>
-      <c r="E9" s="13"/>
-      <c r="F9" s="13"/>
-      <c r="G9" s="13" t="s">
-        <v>154</v>
-      </c>
-      <c r="H9" s="14" t="s">
-        <v>154</v>
-      </c>
-      <c r="I9" s="15" t="s">
-        <v>154</v>
-      </c>
-      <c r="J9" s="13"/>
-      <c r="K9" s="13"/>
-      <c r="L9" s="13" t="s">
-        <v>155</v>
-      </c>
-      <c r="M9" s="13" t="s">
-        <v>155</v>
-      </c>
-      <c r="N9" s="13"/>
-      <c r="O9" s="16"/>
-      <c r="P9" s="12"/>
-      <c r="Q9" s="13" t="s">
-        <v>155</v>
-      </c>
-      <c r="R9" s="13" t="s">
-        <v>155</v>
-      </c>
-      <c r="S9" s="13"/>
-      <c r="T9" s="13"/>
-      <c r="U9" s="13" t="s">
-        <v>155</v>
-      </c>
-      <c r="V9" s="14" t="s">
-        <v>155</v>
-      </c>
-      <c r="W9" s="15" t="s">
-        <v>155</v>
-      </c>
-      <c r="X9" s="13"/>
-      <c r="Y9" s="13"/>
-      <c r="Z9" s="13" t="s">
-        <v>154</v>
-      </c>
-      <c r="AA9" s="13" t="s">
-        <v>154</v>
-      </c>
-      <c r="AB9" s="13"/>
-      <c r="AC9" s="17"/>
-    </row>
-    <row r="10" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="B9" s="16" t="s">
+        <v>152</v>
+      </c>
+      <c r="C9" s="17"/>
+      <c r="D9" s="17"/>
+      <c r="E9" s="17" t="s">
+        <v>152</v>
+      </c>
+      <c r="F9" s="17" t="s">
+        <v>152</v>
+      </c>
+      <c r="G9" s="17"/>
+      <c r="H9" s="18"/>
+      <c r="I9" s="18"/>
+      <c r="J9" s="17" t="s">
+        <v>152</v>
+      </c>
+      <c r="K9" s="17" t="s">
+        <v>152</v>
+      </c>
+      <c r="L9" s="17"/>
+      <c r="M9" s="17"/>
+      <c r="N9" s="17" t="s">
+        <v>152</v>
+      </c>
+      <c r="O9" s="19" t="s">
+        <v>152</v>
+      </c>
+      <c r="P9" s="16" t="s">
+        <v>152</v>
+      </c>
+      <c r="Q9" s="17"/>
+      <c r="R9" s="17"/>
+      <c r="S9" s="17" t="s">
+        <v>152</v>
+      </c>
+      <c r="T9" s="17" t="s">
+        <v>152</v>
+      </c>
+      <c r="U9" s="17"/>
+      <c r="V9" s="18"/>
+      <c r="W9" s="18"/>
+      <c r="X9" s="17" t="s">
+        <v>152</v>
+      </c>
+      <c r="Y9" s="17" t="s">
+        <v>152</v>
+      </c>
+      <c r="Z9" s="17"/>
+      <c r="AA9" s="17"/>
+      <c r="AB9" s="17" t="s">
+        <v>152</v>
+      </c>
+      <c r="AC9" s="19" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="10" spans="1:29" ht="16" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>132</v>
       </c>
-      <c r="B10" s="12" t="s">
-        <v>155</v>
-      </c>
-      <c r="C10" s="13"/>
-      <c r="D10" s="13"/>
-      <c r="E10" s="13" t="s">
-        <v>155</v>
-      </c>
-      <c r="F10" s="13" t="s">
-        <v>155</v>
-      </c>
-      <c r="G10" s="13"/>
-      <c r="H10" s="14"/>
-      <c r="I10" s="15"/>
-      <c r="J10" s="13" t="s">
-        <v>155</v>
-      </c>
-      <c r="K10" s="13" t="s">
-        <v>155</v>
-      </c>
-      <c r="L10" s="13"/>
-      <c r="M10" s="13"/>
-      <c r="N10" s="13" t="s">
-        <v>155</v>
-      </c>
-      <c r="O10" s="16" t="s">
-        <v>155</v>
-      </c>
-      <c r="P10" s="12" t="s">
-        <v>155</v>
-      </c>
-      <c r="Q10" s="13"/>
-      <c r="R10" s="13"/>
-      <c r="S10" s="13" t="s">
-        <v>155</v>
-      </c>
-      <c r="T10" s="13" t="s">
-        <v>155</v>
-      </c>
-      <c r="U10" s="13"/>
-      <c r="V10" s="14"/>
-      <c r="W10" s="15"/>
-      <c r="X10" s="13" t="s">
-        <v>155</v>
-      </c>
-      <c r="Y10" s="13" t="s">
-        <v>155</v>
-      </c>
-      <c r="Z10" s="13"/>
-      <c r="AA10" s="13"/>
-      <c r="AB10" s="13" t="s">
-        <v>155</v>
-      </c>
-      <c r="AC10" s="17" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="11" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="B10" s="16"/>
+      <c r="C10" s="17" t="s">
+        <v>152</v>
+      </c>
+      <c r="D10" s="17" t="s">
+        <v>152</v>
+      </c>
+      <c r="E10" s="17"/>
+      <c r="F10" s="17"/>
+      <c r="G10" s="17" t="s">
+        <v>152</v>
+      </c>
+      <c r="H10" s="18" t="s">
+        <v>152</v>
+      </c>
+      <c r="I10" s="18" t="s">
+        <v>152</v>
+      </c>
+      <c r="J10" s="17"/>
+      <c r="K10" s="17"/>
+      <c r="L10" s="17" t="s">
+        <v>151</v>
+      </c>
+      <c r="M10" s="17" t="s">
+        <v>151</v>
+      </c>
+      <c r="N10" s="17"/>
+      <c r="O10" s="19"/>
+      <c r="P10" s="16"/>
+      <c r="Q10" s="17" t="s">
+        <v>151</v>
+      </c>
+      <c r="R10" s="17" t="s">
+        <v>151</v>
+      </c>
+      <c r="S10" s="17"/>
+      <c r="T10" s="17"/>
+      <c r="U10" s="17" t="s">
+        <v>151</v>
+      </c>
+      <c r="V10" s="18" t="s">
+        <v>151</v>
+      </c>
+      <c r="W10" s="18" t="s">
+        <v>151</v>
+      </c>
+      <c r="X10" s="17"/>
+      <c r="Y10" s="17"/>
+      <c r="Z10" s="17" t="s">
+        <v>152</v>
+      </c>
+      <c r="AA10" s="17" t="s">
+        <v>152</v>
+      </c>
+      <c r="AB10" s="17"/>
+      <c r="AC10" s="19"/>
+    </row>
+    <row r="11" spans="1:29" ht="16" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>133</v>
       </c>
-      <c r="B11" s="12"/>
-      <c r="C11" s="13" t="s">
-        <v>155</v>
-      </c>
-      <c r="D11" s="13" t="s">
-        <v>155</v>
-      </c>
-      <c r="E11" s="13"/>
-      <c r="F11" s="13"/>
-      <c r="G11" s="13" t="s">
-        <v>155</v>
-      </c>
-      <c r="H11" s="14" t="s">
-        <v>155</v>
-      </c>
-      <c r="I11" s="15" t="s">
-        <v>155</v>
-      </c>
-      <c r="J11" s="13"/>
-      <c r="K11" s="13"/>
-      <c r="L11" s="13" t="s">
-        <v>154</v>
-      </c>
-      <c r="M11" s="13" t="s">
-        <v>154</v>
-      </c>
-      <c r="N11" s="13"/>
-      <c r="O11" s="16"/>
-      <c r="P11" s="12"/>
-      <c r="Q11" s="13" t="s">
-        <v>154</v>
-      </c>
-      <c r="R11" s="13" t="s">
-        <v>154</v>
-      </c>
-      <c r="S11" s="13"/>
-      <c r="T11" s="13"/>
-      <c r="U11" s="13" t="s">
-        <v>154</v>
-      </c>
-      <c r="V11" s="14" t="s">
-        <v>154</v>
-      </c>
-      <c r="W11" s="15" t="s">
-        <v>154</v>
-      </c>
-      <c r="X11" s="13"/>
-      <c r="Y11" s="13"/>
-      <c r="Z11" s="13" t="s">
-        <v>155</v>
-      </c>
-      <c r="AA11" s="13" t="s">
-        <v>155</v>
-      </c>
-      <c r="AB11" s="13"/>
-      <c r="AC11" s="17"/>
-    </row>
-    <row r="12" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="B11" s="16" t="s">
+        <v>153</v>
+      </c>
+      <c r="C11" s="17"/>
+      <c r="D11" s="17"/>
+      <c r="E11" s="17" t="s">
+        <v>153</v>
+      </c>
+      <c r="F11" s="17" t="s">
+        <v>153</v>
+      </c>
+      <c r="G11" s="17"/>
+      <c r="H11" s="18"/>
+      <c r="I11" s="18"/>
+      <c r="J11" s="17" t="s">
+        <v>153</v>
+      </c>
+      <c r="K11" s="17" t="s">
+        <v>153</v>
+      </c>
+      <c r="L11" s="17"/>
+      <c r="M11" s="17"/>
+      <c r="N11" s="17" t="s">
+        <v>153</v>
+      </c>
+      <c r="O11" s="19" t="s">
+        <v>153</v>
+      </c>
+      <c r="P11" s="16" t="s">
+        <v>153</v>
+      </c>
+      <c r="Q11" s="17"/>
+      <c r="R11" s="17"/>
+      <c r="S11" s="17" t="s">
+        <v>153</v>
+      </c>
+      <c r="T11" s="17" t="s">
+        <v>153</v>
+      </c>
+      <c r="U11" s="17"/>
+      <c r="V11" s="18"/>
+      <c r="W11" s="18"/>
+      <c r="X11" s="17" t="s">
+        <v>153</v>
+      </c>
+      <c r="Y11" s="17" t="s">
+        <v>153</v>
+      </c>
+      <c r="Z11" s="17"/>
+      <c r="AA11" s="17"/>
+      <c r="AB11" s="17" t="s">
+        <v>153</v>
+      </c>
+      <c r="AC11" s="19" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="12" spans="1:29" ht="16" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>134</v>
       </c>
-      <c r="B12" s="12" t="s">
-        <v>156</v>
-      </c>
-      <c r="C12" s="13"/>
-      <c r="D12" s="13"/>
-      <c r="E12" s="13" t="s">
-        <v>156</v>
-      </c>
-      <c r="F12" s="13" t="s">
-        <v>156</v>
-      </c>
-      <c r="G12" s="13"/>
-      <c r="H12" s="14"/>
-      <c r="I12" s="15"/>
-      <c r="J12" s="13" t="s">
-        <v>156</v>
-      </c>
-      <c r="K12" s="13" t="s">
-        <v>156</v>
-      </c>
-      <c r="L12" s="13"/>
-      <c r="M12" s="13"/>
-      <c r="N12" s="13" t="s">
-        <v>156</v>
-      </c>
-      <c r="O12" s="16" t="s">
-        <v>156</v>
-      </c>
-      <c r="P12" s="12" t="s">
-        <v>156</v>
-      </c>
-      <c r="Q12" s="13"/>
-      <c r="R12" s="13"/>
-      <c r="S12" s="13" t="s">
-        <v>156</v>
-      </c>
-      <c r="T12" s="13" t="s">
-        <v>156</v>
-      </c>
-      <c r="U12" s="13"/>
-      <c r="V12" s="14"/>
-      <c r="W12" s="15"/>
-      <c r="X12" s="13" t="s">
-        <v>156</v>
-      </c>
-      <c r="Y12" s="13" t="s">
-        <v>156</v>
-      </c>
-      <c r="Z12" s="13"/>
-      <c r="AA12" s="13"/>
-      <c r="AB12" s="13" t="s">
-        <v>156</v>
-      </c>
-      <c r="AC12" s="17" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="13" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="B12" s="16" t="s">
+        <v>149</v>
+      </c>
+      <c r="C12" s="17"/>
+      <c r="D12" s="17"/>
+      <c r="E12" s="17" t="s">
+        <v>149</v>
+      </c>
+      <c r="F12" s="17" t="s">
+        <v>149</v>
+      </c>
+      <c r="G12" s="17"/>
+      <c r="H12" s="18"/>
+      <c r="I12" s="18"/>
+      <c r="J12" s="17" t="s">
+        <v>148</v>
+      </c>
+      <c r="K12" s="17" t="s">
+        <v>148</v>
+      </c>
+      <c r="L12" s="17"/>
+      <c r="M12" s="17"/>
+      <c r="N12" s="17" t="s">
+        <v>148</v>
+      </c>
+      <c r="O12" s="19" t="s">
+        <v>148</v>
+      </c>
+      <c r="P12" s="16" t="s">
+        <v>148</v>
+      </c>
+      <c r="Q12" s="17"/>
+      <c r="R12" s="17"/>
+      <c r="S12" s="17" t="s">
+        <v>148</v>
+      </c>
+      <c r="T12" s="17" t="s">
+        <v>148</v>
+      </c>
+      <c r="U12" s="17"/>
+      <c r="V12" s="18"/>
+      <c r="W12" s="18"/>
+      <c r="X12" s="17" t="s">
+        <v>149</v>
+      </c>
+      <c r="Y12" s="17" t="s">
+        <v>149</v>
+      </c>
+      <c r="Z12" s="17"/>
+      <c r="AA12" s="17"/>
+      <c r="AB12" s="17" t="s">
+        <v>149</v>
+      </c>
+      <c r="AC12" s="19" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="13" spans="1:29" ht="16" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>135</v>
       </c>
-      <c r="B13" s="12" t="s">
+      <c r="B13" s="16" t="s">
         <v>151</v>
       </c>
-      <c r="C13" s="13"/>
-      <c r="D13" s="13"/>
-      <c r="E13" s="13" t="s">
+      <c r="C13" s="17"/>
+      <c r="D13" s="17"/>
+      <c r="E13" s="17" t="s">
         <v>151</v>
       </c>
-      <c r="F13" s="13" t="s">
+      <c r="F13" s="17" t="s">
         <v>151</v>
       </c>
-      <c r="G13" s="13"/>
-      <c r="H13" s="14"/>
-      <c r="I13" s="15"/>
-      <c r="J13" s="13" t="s">
-        <v>150</v>
-      </c>
-      <c r="K13" s="13" t="s">
-        <v>150</v>
-      </c>
-      <c r="L13" s="13"/>
-      <c r="M13" s="13"/>
-      <c r="N13" s="13" t="s">
-        <v>150</v>
-      </c>
-      <c r="O13" s="16" t="s">
-        <v>150</v>
-      </c>
-      <c r="P13" s="12" t="s">
-        <v>150</v>
-      </c>
-      <c r="Q13" s="13"/>
-      <c r="R13" s="13"/>
-      <c r="S13" s="13" t="s">
-        <v>150</v>
-      </c>
-      <c r="T13" s="13" t="s">
-        <v>150</v>
-      </c>
-      <c r="U13" s="13"/>
-      <c r="V13" s="14"/>
-      <c r="W13" s="15"/>
-      <c r="X13" s="13" t="s">
+      <c r="G13" s="17"/>
+      <c r="H13" s="18"/>
+      <c r="I13" s="18"/>
+      <c r="J13" s="17" t="s">
         <v>151</v>
       </c>
-      <c r="Y13" s="13" t="s">
+      <c r="K13" s="17" t="s">
         <v>151</v>
       </c>
-      <c r="Z13" s="13"/>
-      <c r="AA13" s="13"/>
-      <c r="AB13" s="13" t="s">
+      <c r="L13" s="17"/>
+      <c r="M13" s="17"/>
+      <c r="N13" s="17" t="s">
         <v>151</v>
       </c>
-      <c r="AC13" s="17" t="s">
+      <c r="O13" s="19" t="s">
         <v>151</v>
       </c>
-    </row>
-    <row r="14" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="P13" s="16" t="s">
+        <v>151</v>
+      </c>
+      <c r="Q13" s="17"/>
+      <c r="R13" s="17"/>
+      <c r="S13" s="17" t="s">
+        <v>151</v>
+      </c>
+      <c r="T13" s="17" t="s">
+        <v>151</v>
+      </c>
+      <c r="U13" s="17"/>
+      <c r="V13" s="18"/>
+      <c r="W13" s="18"/>
+      <c r="X13" s="17" t="s">
+        <v>151</v>
+      </c>
+      <c r="Y13" s="17" t="s">
+        <v>151</v>
+      </c>
+      <c r="Z13" s="17"/>
+      <c r="AA13" s="17"/>
+      <c r="AB13" s="17" t="s">
+        <v>151</v>
+      </c>
+      <c r="AC13" s="19" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="14" spans="1:29" ht="16" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>136</v>
       </c>
-      <c r="B14" s="12" t="s">
-        <v>154</v>
-      </c>
-      <c r="C14" s="13"/>
-      <c r="D14" s="13"/>
-      <c r="E14" s="13" t="s">
-        <v>154</v>
-      </c>
-      <c r="F14" s="13" t="s">
-        <v>154</v>
-      </c>
-      <c r="G14" s="13"/>
-      <c r="H14" s="14"/>
-      <c r="I14" s="15"/>
-      <c r="J14" s="13" t="s">
-        <v>154</v>
-      </c>
-      <c r="K14" s="13" t="s">
-        <v>154</v>
-      </c>
-      <c r="L14" s="13"/>
-      <c r="M14" s="13"/>
-      <c r="N14" s="13" t="s">
-        <v>154</v>
-      </c>
-      <c r="O14" s="16" t="s">
-        <v>154</v>
-      </c>
-      <c r="P14" s="12" t="s">
-        <v>154</v>
-      </c>
-      <c r="Q14" s="13"/>
-      <c r="R14" s="13"/>
-      <c r="S14" s="13" t="s">
-        <v>154</v>
-      </c>
-      <c r="T14" s="13" t="s">
-        <v>154</v>
-      </c>
-      <c r="U14" s="13"/>
-      <c r="V14" s="14"/>
-      <c r="W14" s="15"/>
-      <c r="X14" s="13" t="s">
-        <v>154</v>
-      </c>
-      <c r="Y14" s="13" t="s">
-        <v>154</v>
-      </c>
-      <c r="Z14" s="13"/>
-      <c r="AA14" s="13"/>
-      <c r="AB14" s="13" t="s">
-        <v>154</v>
-      </c>
-      <c r="AC14" s="17" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="15" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="B14" s="16" t="s">
+        <v>148</v>
+      </c>
+      <c r="C14" s="17"/>
+      <c r="D14" s="17"/>
+      <c r="E14" s="17" t="s">
+        <v>148</v>
+      </c>
+      <c r="F14" s="17" t="s">
+        <v>148</v>
+      </c>
+      <c r="G14" s="17"/>
+      <c r="H14" s="18"/>
+      <c r="I14" s="18"/>
+      <c r="J14" s="17" t="s">
+        <v>149</v>
+      </c>
+      <c r="K14" s="17" t="s">
+        <v>149</v>
+      </c>
+      <c r="L14" s="17"/>
+      <c r="M14" s="17"/>
+      <c r="N14" s="17" t="s">
+        <v>149</v>
+      </c>
+      <c r="O14" s="19" t="s">
+        <v>149</v>
+      </c>
+      <c r="P14" s="16" t="s">
+        <v>149</v>
+      </c>
+      <c r="Q14" s="17"/>
+      <c r="R14" s="17"/>
+      <c r="S14" s="17" t="s">
+        <v>149</v>
+      </c>
+      <c r="T14" s="17" t="s">
+        <v>149</v>
+      </c>
+      <c r="U14" s="17"/>
+      <c r="V14" s="18"/>
+      <c r="W14" s="18"/>
+      <c r="X14" s="17" t="s">
+        <v>148</v>
+      </c>
+      <c r="Y14" s="17" t="s">
+        <v>148</v>
+      </c>
+      <c r="Z14" s="17"/>
+      <c r="AA14" s="17"/>
+      <c r="AB14" s="17" t="s">
+        <v>148</v>
+      </c>
+      <c r="AC14" s="19" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="15" spans="1:29" ht="16" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>137</v>
       </c>
-      <c r="B15" s="12" t="s">
-        <v>150</v>
-      </c>
-      <c r="C15" s="13"/>
-      <c r="D15" s="13"/>
-      <c r="E15" s="13" t="s">
-        <v>150</v>
-      </c>
-      <c r="F15" s="13" t="s">
-        <v>150</v>
-      </c>
-      <c r="G15" s="13"/>
-      <c r="H15" s="14"/>
-      <c r="I15" s="15"/>
-      <c r="J15" s="13" t="s">
-        <v>151</v>
-      </c>
-      <c r="K15" s="13" t="s">
-        <v>151</v>
-      </c>
-      <c r="L15" s="13"/>
-      <c r="M15" s="13"/>
-      <c r="N15" s="13" t="s">
-        <v>151</v>
-      </c>
-      <c r="O15" s="16" t="s">
-        <v>151</v>
-      </c>
-      <c r="P15" s="12" t="s">
-        <v>151</v>
-      </c>
-      <c r="Q15" s="13"/>
-      <c r="R15" s="13"/>
-      <c r="S15" s="13" t="s">
-        <v>151</v>
-      </c>
-      <c r="T15" s="13" t="s">
-        <v>151</v>
-      </c>
-      <c r="U15" s="13"/>
-      <c r="V15" s="14"/>
-      <c r="W15" s="15"/>
-      <c r="X15" s="13" t="s">
-        <v>150</v>
-      </c>
-      <c r="Y15" s="13" t="s">
-        <v>150</v>
-      </c>
-      <c r="Z15" s="13"/>
-      <c r="AA15" s="13"/>
-      <c r="AB15" s="13" t="s">
-        <v>150</v>
-      </c>
-      <c r="AC15" s="17" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="16" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="B15" s="16"/>
+      <c r="C15" s="17" t="s">
+        <v>153</v>
+      </c>
+      <c r="D15" s="17" t="s">
+        <v>153</v>
+      </c>
+      <c r="E15" s="17"/>
+      <c r="F15" s="17"/>
+      <c r="G15" s="17" t="s">
+        <v>153</v>
+      </c>
+      <c r="H15" s="18" t="s">
+        <v>153</v>
+      </c>
+      <c r="I15" s="18" t="s">
+        <v>153</v>
+      </c>
+      <c r="J15" s="17"/>
+      <c r="K15" s="17"/>
+      <c r="L15" s="17" t="s">
+        <v>153</v>
+      </c>
+      <c r="M15" s="17" t="s">
+        <v>153</v>
+      </c>
+      <c r="N15" s="17"/>
+      <c r="O15" s="19"/>
+      <c r="P15" s="16"/>
+      <c r="Q15" s="17" t="s">
+        <v>153</v>
+      </c>
+      <c r="R15" s="17" t="s">
+        <v>153</v>
+      </c>
+      <c r="S15" s="17"/>
+      <c r="T15" s="17"/>
+      <c r="U15" s="17" t="s">
+        <v>153</v>
+      </c>
+      <c r="V15" s="18" t="s">
+        <v>153</v>
+      </c>
+      <c r="W15" s="18" t="s">
+        <v>153</v>
+      </c>
+      <c r="X15" s="17"/>
+      <c r="Y15" s="17"/>
+      <c r="Z15" s="17" t="s">
+        <v>153</v>
+      </c>
+      <c r="AA15" s="17" t="s">
+        <v>153</v>
+      </c>
+      <c r="AB15" s="17"/>
+      <c r="AC15" s="19"/>
+    </row>
+    <row r="16" spans="1:29" ht="16" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
+        <v>159</v>
+      </c>
+      <c r="B16" s="20" t="s">
+        <v>146</v>
+      </c>
+      <c r="C16" s="21"/>
+      <c r="D16" s="21"/>
+      <c r="E16" s="21" t="s">
+        <v>146</v>
+      </c>
+      <c r="F16" s="21" t="s">
+        <v>146</v>
+      </c>
+      <c r="G16" s="21"/>
+      <c r="H16" s="22"/>
+      <c r="I16" s="22"/>
+      <c r="J16" s="21" t="s">
+        <v>146</v>
+      </c>
+      <c r="K16" s="21" t="s">
+        <v>146</v>
+      </c>
+      <c r="L16" s="21"/>
+      <c r="M16" s="21"/>
+      <c r="N16" s="21" t="s">
+        <v>147</v>
+      </c>
+      <c r="O16" s="23" t="s">
+        <v>147</v>
+      </c>
+      <c r="P16" s="20" t="s">
+        <v>147</v>
+      </c>
+      <c r="Q16" s="21"/>
+      <c r="R16" s="21"/>
+      <c r="S16" s="21" t="s">
+        <v>147</v>
+      </c>
+      <c r="T16" s="21" t="s">
+        <v>147</v>
+      </c>
+      <c r="U16" s="21"/>
+      <c r="V16" s="22"/>
+      <c r="W16" s="22"/>
+      <c r="X16" s="21" t="s">
+        <v>147</v>
+      </c>
+      <c r="Y16" s="21" t="s">
+        <v>147</v>
+      </c>
+      <c r="Z16" s="21"/>
+      <c r="AA16" s="21"/>
+      <c r="AB16" s="21" t="s">
+        <v>146</v>
+      </c>
+      <c r="AC16" s="23" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="17" spans="1:29" ht="16" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
         <v>138</v>
       </c>
-      <c r="B16" s="12"/>
-      <c r="C16" s="13" t="s">
-        <v>156</v>
-      </c>
-      <c r="D16" s="13" t="s">
-        <v>156</v>
-      </c>
-      <c r="E16" s="13"/>
-      <c r="F16" s="13"/>
-      <c r="G16" s="13" t="s">
-        <v>156</v>
-      </c>
-      <c r="H16" s="14" t="s">
-        <v>156</v>
-      </c>
-      <c r="I16" s="15" t="s">
-        <v>156</v>
-      </c>
-      <c r="J16" s="13"/>
-      <c r="K16" s="13"/>
-      <c r="L16" s="13" t="s">
-        <v>156</v>
-      </c>
-      <c r="M16" s="13" t="s">
-        <v>156</v>
-      </c>
-      <c r="N16" s="13"/>
-      <c r="O16" s="16"/>
-      <c r="P16" s="12"/>
-      <c r="Q16" s="13" t="s">
-        <v>156</v>
-      </c>
-      <c r="R16" s="13" t="s">
-        <v>156</v>
-      </c>
-      <c r="S16" s="13"/>
-      <c r="T16" s="13"/>
-      <c r="U16" s="13" t="s">
-        <v>156</v>
-      </c>
-      <c r="V16" s="14" t="s">
-        <v>156</v>
-      </c>
-      <c r="W16" s="15" t="s">
-        <v>156</v>
-      </c>
-      <c r="X16" s="13"/>
-      <c r="Y16" s="13"/>
-      <c r="Z16" s="13" t="s">
-        <v>156</v>
-      </c>
-      <c r="AA16" s="13" t="s">
-        <v>156</v>
-      </c>
-      <c r="AB16" s="13"/>
-      <c r="AC16" s="17"/>
-    </row>
-    <row r="17" spans="1:29" x14ac:dyDescent="0.2">
-      <c r="A17" t="s">
-        <v>139</v>
-      </c>
-      <c r="B17" s="12"/>
-      <c r="C17" s="13" t="s">
-        <v>151</v>
-      </c>
-      <c r="D17" s="13" t="s">
-        <v>151</v>
-      </c>
-      <c r="E17" s="13"/>
-      <c r="F17" s="13"/>
-      <c r="G17" s="13" t="s">
-        <v>151</v>
-      </c>
-      <c r="H17" s="14" t="s">
-        <v>151</v>
-      </c>
-      <c r="I17" s="15" t="s">
-        <v>151</v>
-      </c>
-      <c r="J17" s="13"/>
-      <c r="K17" s="13"/>
-      <c r="L17" s="13" t="s">
-        <v>150</v>
-      </c>
-      <c r="M17" s="13" t="s">
-        <v>150</v>
-      </c>
-      <c r="N17" s="13"/>
-      <c r="O17" s="16"/>
-      <c r="P17" s="12"/>
-      <c r="Q17" s="13" t="s">
-        <v>150</v>
-      </c>
-      <c r="R17" s="13" t="s">
-        <v>150</v>
-      </c>
-      <c r="S17" s="13"/>
-      <c r="T17" s="13"/>
-      <c r="U17" s="13" t="s">
-        <v>150</v>
-      </c>
-      <c r="V17" s="14" t="s">
-        <v>150</v>
-      </c>
-      <c r="W17" s="15" t="s">
-        <v>150</v>
-      </c>
-      <c r="X17" s="13"/>
-      <c r="Y17" s="13"/>
-      <c r="Z17" s="13" t="s">
-        <v>151</v>
-      </c>
-      <c r="AA17" s="13" t="s">
-        <v>151</v>
-      </c>
-      <c r="AB17" s="13"/>
-      <c r="AC17" s="17"/>
-    </row>
-    <row r="18" spans="1:29" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>140</v>
-      </c>
-      <c r="B18" s="18"/>
-      <c r="C18" s="19" t="s">
-        <v>152</v>
-      </c>
-      <c r="D18" s="19" t="s">
-        <v>152</v>
-      </c>
-      <c r="E18" s="19"/>
-      <c r="F18" s="19"/>
-      <c r="G18" s="19" t="s">
-        <v>152</v>
-      </c>
-      <c r="H18" s="20" t="s">
-        <v>152</v>
-      </c>
-      <c r="I18" s="21" t="s">
-        <v>152</v>
-      </c>
-      <c r="J18" s="19"/>
-      <c r="K18" s="19"/>
-      <c r="L18" s="19" t="s">
-        <v>152</v>
-      </c>
-      <c r="M18" s="19" t="s">
-        <v>152</v>
-      </c>
-      <c r="N18" s="19"/>
-      <c r="O18" s="22"/>
-      <c r="P18" s="18"/>
-      <c r="Q18" s="19" t="s">
-        <v>152</v>
-      </c>
-      <c r="R18" s="19" t="s">
-        <v>152</v>
-      </c>
-      <c r="S18" s="19"/>
-      <c r="T18" s="19"/>
-      <c r="U18" s="19" t="s">
-        <v>152</v>
-      </c>
-      <c r="V18" s="20" t="s">
-        <v>152</v>
-      </c>
-      <c r="W18" s="21" t="s">
-        <v>152</v>
-      </c>
-      <c r="X18" s="19"/>
-      <c r="Y18" s="19"/>
-      <c r="Z18" s="19" t="s">
-        <v>152</v>
-      </c>
-      <c r="AA18" s="19" t="s">
-        <v>152</v>
-      </c>
-      <c r="AB18" s="19"/>
-      <c r="AC18" s="23"/>
+      <c r="B17" s="16"/>
+      <c r="C17" s="17" t="s">
+        <v>149</v>
+      </c>
+      <c r="D17" s="17" t="s">
+        <v>149</v>
+      </c>
+      <c r="E17" s="17"/>
+      <c r="F17" s="17"/>
+      <c r="G17" s="17" t="s">
+        <v>149</v>
+      </c>
+      <c r="H17" s="18" t="s">
+        <v>149</v>
+      </c>
+      <c r="I17" s="18" t="s">
+        <v>149</v>
+      </c>
+      <c r="J17" s="17"/>
+      <c r="K17" s="17"/>
+      <c r="L17" s="17" t="s">
+        <v>149</v>
+      </c>
+      <c r="M17" s="17" t="s">
+        <v>149</v>
+      </c>
+      <c r="N17" s="17"/>
+      <c r="O17" s="19"/>
+      <c r="P17" s="16"/>
+      <c r="Q17" s="17" t="s">
+        <v>149</v>
+      </c>
+      <c r="R17" s="17" t="s">
+        <v>149</v>
+      </c>
+      <c r="S17" s="17"/>
+      <c r="T17" s="17"/>
+      <c r="U17" s="17" t="s">
+        <v>149</v>
+      </c>
+      <c r="V17" s="18" t="s">
+        <v>149</v>
+      </c>
+      <c r="W17" s="18" t="s">
+        <v>149</v>
+      </c>
+      <c r="X17" s="17"/>
+      <c r="Y17" s="17"/>
+      <c r="Z17" s="17" t="s">
+        <v>149</v>
+      </c>
+      <c r="AA17" s="17" t="s">
+        <v>149</v>
+      </c>
+      <c r="AB17" s="17"/>
+      <c r="AC17" s="19"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6249,6 +6200,23 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_Flow_SignoffStatus xmlns="3ae64878-e7bb-4c65-a932-4cdc61fbe63f" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009F702E5FD63918449A87815BC57997B4" ma:contentTypeVersion="7" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="f366023269454ced43510f73883a6d91">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="3ae64878-e7bb-4c65-a932-4cdc61fbe63f" xmlns:ns3="b0d30a24-05e2-4154-8fed-e579ddd987b0" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="dd01e2e1f35a8420c36650a8355a0ef6" ns2:_="" ns3:_="">
     <xsd:import namespace="3ae64878-e7bb-4c65-a932-4cdc61fbe63f"/>
@@ -6431,24 +6399,25 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_Flow_SignoffStatus xmlns="3ae64878-e7bb-4c65-a932-4cdc61fbe63f" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9EFFDED6-61B9-426A-8C57-4EB4CD0F4E95}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4ED2462D-4DC3-4D8C-9537-7DD0B7423608}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="3ae64878-e7bb-4c65-a932-4cdc61fbe63f"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2DEFF9ED-23D7-4EA5-99B7-575064A65984}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -6465,22 +6434,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4ED2462D-4DC3-4D8C-9537-7DD0B7423608}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="3ae64878-e7bb-4c65-a932-4cdc61fbe63f"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9EFFDED6-61B9-426A-8C57-4EB4CD0F4E95}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>